--- a/Chau/status1.xlsx
+++ b/Chau/status1.xlsx
@@ -9,21 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8085"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="8085" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="learning resources" sheetId="2" r:id="rId1"/>
-    <sheet name="assignment" sheetId="1" r:id="rId2"/>
+    <sheet name="Learning resources" sheetId="2" r:id="rId1"/>
+    <sheet name="Assignment" sheetId="1" r:id="rId2"/>
+    <sheet name="Member" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="28" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="148">
   <si>
     <t>Task_Name</t>
   </si>
@@ -428,13 +429,52 @@
   </si>
   <si>
     <t>Count of Status</t>
+  </si>
+  <si>
+    <t>taib2504893@student.ctu.edu.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Tài</t>
+  </si>
+  <si>
+    <t>chaub2504867@student.ctu.edu.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Châu</t>
+  </si>
+  <si>
+    <t>chuongB2504868@student.ctu.edu.vn</t>
+  </si>
+  <si>
+    <t>Nguyễn Phúc Nguyên Chương</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tranleminhkhoi1510@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trần Lê Minh Khôi </t>
+  </si>
+  <si>
+    <t>manb2504882@student.ctu.edu.vn</t>
+  </si>
+  <si>
+    <t>Ngô Triệu Mẫn</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Mem_Name</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -446,6 +486,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="163"/>
     </font>
   </fonts>
   <fills count="2">
@@ -483,7 +530,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -492,6 +539,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -710,7 +758,6 @@
         <c:idx val="12"/>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -747,9 +794,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -981,7 +1026,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[status1.xlsx]assignment!PivotTable17</c:name>
+    <c:name>[status1.xlsx]Assignment!PivotTable17</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1052,7 +1097,6 @@
         <c:idx val="2"/>
         <c:dLbl>
           <c:idx val="0"/>
-          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1089,9 +1133,7 @@
           <c:showPercent val="1"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-              <c15:layout/>
-            </c:ext>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -1110,6 +1152,69 @@
           <c:symbol val="none"/>
         </c:marker>
       </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
@@ -1120,7 +1225,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>assignment!$B$31</c:f>
+              <c:f>Assignment!$B$31</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1141,6 +1246,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-2CD0-4294-AF03-EA12C8203996}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
@@ -1154,6 +1264,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-2CD0-4294-AF03-EA12C8203996}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
@@ -1167,6 +1282,11 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-2CD0-4294-AF03-EA12C8203996}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
@@ -1180,13 +1300,18 @@
               </a:ln>
               <a:effectLst/>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-2CD0-4294-AF03-EA12C8203996}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:delete val="1"/>
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>assignment!$A$32:$A$36</c:f>
+              <c:f>Assignment!$A$32:$A$36</c:f>
               <c:strCache>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
@@ -1206,7 +1331,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>assignment!$B$32:$B$36</c:f>
+              <c:f>Assignment!$B$32:$B$36</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
@@ -2430,7 +2555,7 @@
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
+      <xdr:col>6</xdr:col>
       <xdr:colOff>638734</xdr:colOff>
       <xdr:row>54</xdr:row>
       <xdr:rowOff>168087</xdr:rowOff>
@@ -2458,7 +2583,7 @@
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="ADMIN" refreshedDate="46097.777464236111" createdVersion="6" refreshedVersion="6" minRefreshableVersion="3" recordCount="28">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A1:H29" sheet="assignment"/>
+    <worksheetSource ref="A1:I29" sheet="Assignment"/>
   </cacheSource>
   <cacheFields count="8">
     <cacheField name=" bbvvvvD/g" numFmtId="0">
@@ -2785,7 +2910,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable17" cacheId="28" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable17" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A31:B36" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="8">
     <pivotField showAll="0"/>
@@ -2831,6 +2956,65 @@
   <dataFields count="1">
     <dataField name="Count of Status" fld="7" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="0" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="8">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="7" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3406,19 +3590,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" customWidth="1"/>
     <col min="3" max="3" width="121.5703125" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="5" max="5" width="49.5703125" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" customWidth="1"/>
+    <col min="8" max="8" width="16.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>96</v>
       </c>
@@ -3431,20 +3617,23 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3457,20 +3646,24 @@
       <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="2" t="str">
+        <f>VLOOKUP(D2, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>15</v>
       </c>
@@ -3483,20 +3676,24 @@
       <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="2" t="str">
+        <f>VLOOKUP(D3, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
@@ -3509,20 +3706,24 @@
       <c r="D4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="2" t="str">
+        <f>VLOOKUP(D4, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
@@ -3535,20 +3736,24 @@
       <c r="D5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="2" t="str">
+        <f>VLOOKUP(D5, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
@@ -3561,20 +3766,24 @@
       <c r="D6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="2" t="str">
+        <f>VLOOKUP(D6, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Phúc Nguyên Chương</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
@@ -3587,20 +3796,24 @@
       <c r="D7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="2" t="str">
+        <f>VLOOKUP(D7, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Phúc Nguyên Chương</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>34</v>
       </c>
@@ -3613,20 +3826,24 @@
       <c r="D8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="2" t="str">
+        <f>VLOOKUP(D8, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>38</v>
       </c>
@@ -3639,20 +3856,24 @@
       <c r="D9" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="2" t="str">
+        <f>VLOOKUP(D9, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Ngọc Châu</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>43</v>
       </c>
@@ -3665,20 +3886,24 @@
       <c r="D10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="2" t="str">
+        <f>VLOOKUP(D10, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Ngọc Châu</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="2" t="s">
+      <c r="I10" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>46</v>
       </c>
@@ -3691,20 +3916,24 @@
       <c r="D11" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="2" t="str">
+        <f>VLOOKUP(D11, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>50</v>
       </c>
@@ -3717,20 +3946,24 @@
       <c r="D12" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="2" t="str">
+        <f>VLOOKUP(D12, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Ngọc Châu</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="G12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>54</v>
       </c>
@@ -3743,20 +3976,24 @@
       <c r="D13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="2" t="str">
+        <f>VLOOKUP(D13, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Ngọc Châu</v>
+      </c>
+      <c r="F13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="G13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="H13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>57</v>
       </c>
@@ -3769,20 +4006,24 @@
       <c r="D14" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="2" t="str">
+        <f>VLOOKUP(D14, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="G14" s="2" t="s">
+      <c r="H14" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>62</v>
       </c>
@@ -3795,20 +4036,24 @@
       <c r="D15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="2" t="str">
+        <f>VLOOKUP(D15, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="H15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="2" t="s">
+      <c r="I15" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>66</v>
       </c>
@@ -3821,20 +4066,24 @@
       <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="2" t="str">
+        <f>VLOOKUP(D16, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Ngọc Châu</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H16" s="2" t="s">
+      <c r="I16" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>69</v>
       </c>
@@ -3847,20 +4096,24 @@
       <c r="D17" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="2" t="str">
+        <f>VLOOKUP(D17, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>74</v>
       </c>
@@ -3873,20 +4126,24 @@
       <c r="D18" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" s="2" t="str">
+        <f>VLOOKUP(D18, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>77</v>
       </c>
@@ -3899,20 +4156,24 @@
       <c r="D19" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="2" t="str">
+        <f>VLOOKUP(D19, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
@@ -3925,20 +4186,24 @@
       <c r="D20" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="2" t="str">
+        <f>VLOOKUP(D20, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="G20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="2" t="s">
+      <c r="H20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="2" t="s">
+      <c r="I20" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>85</v>
       </c>
@@ -3951,20 +4216,24 @@
       <c r="D21" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="2" t="str">
+        <f>VLOOKUP(D21, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="G21" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="H21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>88</v>
       </c>
@@ -3977,20 +4246,24 @@
       <c r="D22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="2" t="str">
+        <f>VLOOKUP(D22, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Phúc Nguyên Chương</v>
+      </c>
+      <c r="F22" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="G22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="H22" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H22" s="2" t="s">
+      <c r="I22" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>89</v>
       </c>
@@ -4003,20 +4276,24 @@
       <c r="D23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" s="2" t="str">
+        <f>VLOOKUP(D23, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="G23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="I23" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>90</v>
       </c>
@@ -4029,20 +4306,24 @@
       <c r="D24" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" s="2" t="str">
+        <f>VLOOKUP(D24, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="G24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="H24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>91</v>
       </c>
@@ -4055,20 +4336,24 @@
       <c r="D25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" s="2" t="str">
+        <f>VLOOKUP(D25, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G25" s="2" t="s">
+      <c r="H25" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H25" s="2" t="s">
+      <c r="I25" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>92</v>
       </c>
@@ -4081,20 +4366,24 @@
       <c r="D26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="2" t="str">
+        <f>VLOOKUP(D26, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Phúc Nguyên Chương</v>
+      </c>
+      <c r="F26" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H26" s="2" t="s">
+      <c r="I26" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>93</v>
       </c>
@@ -4107,20 +4396,24 @@
       <c r="D27" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="2" t="str">
+        <f>VLOOKUP(D27, Member!$A$2:$C$6, 2, 0)</f>
+        <v xml:space="preserve">Trần Lê Minh Khôi </v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="H27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>94</v>
       </c>
@@ -4133,20 +4426,24 @@
       <c r="D28" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="2" t="str">
+        <f>VLOOKUP(D28, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Ngô Triệu Mẫn</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="G28" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G28" s="2" t="s">
+      <c r="H28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H28" s="2" t="s">
+      <c r="I28" s="2" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>95</v>
       </c>
@@ -4159,20 +4456,24 @@
       <c r="D29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" s="2" t="str">
+        <f>VLOOKUP(D29, Member!$A$2:$C$6, 2, 0)</f>
+        <v>Nguyễn Thành Tài</v>
+      </c>
+      <c r="F29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="G29" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>132</v>
       </c>
@@ -4180,7 +4481,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>14</v>
       </c>
@@ -4222,6 +4523,87 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>